--- a/nursing/フォーマット/03_就労支援記録様式/07_工賃台帳（B型）.xlsx
+++ b/nursing/フォーマット/03_就労支援記録様式/07_工賃台帳（B型）.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工賃台帳" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工賃台帳B型" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,46 +26,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="8"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="00DC2626"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,21 +74,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00A9854A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -97,38 +102,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,388 +536,278 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>工賃台帳（就労継続支援B型用）　　　　年　　月分</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>工賃台帳（就労継続支援B型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【法的根拠】障害者総合支援法 第43条 / 目標工賃：前年度平均工賃月額が目標値以上で「目標工賃達成加算（10単位/日）」を算定可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t xml:space="preserve">　　年度／利用者ごとの月別工賃を記録。平均工賃月額は基本報酬区分・目標工賃達成加算の根拠</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>利用者別 月額工賃（円）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>利用日数</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>作業時間
-合計（h）</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>作業種別（主な作業）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>工賃単価
-（円/h）</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>当月工賃（円）</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>累計工賃
-（年度内）</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>支払日・確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>山田 太郎</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>封入作業・箱折り</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>2026/5/25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>佐藤 花子</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>清掃・洗濯補助</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026/5/25</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>上半期計</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="8" customHeight="1"/>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>当年度 平均工賃月額</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　円　（＝工賃総額 ÷ 延べ利用者数）</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>前年度実績 / 目標工賃</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>月間合計</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>平均工賃月額 = 月間工賃支払総額 ÷ 当月の利用者数　　【目標：月額3,000円以上（努力義務）】</t>
-        </is>
-      </c>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>目標工賃達成加算</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>□算定（10単位/日・前年度平均が目標以上）　□算定なし</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>※ 平均工賃月額は「工賃総支払額 ÷ 利用者延べ人数」で算定。月額3,000円以上が支払いの下限目安。工賃向上計画を都道府県へ提出し、達成で目標工賃達成加算（10単位/日）。</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A27:H27"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>